--- a/output/2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx
@@ -494,7 +494,6 @@
           <t>+381 63 59 33 22 (ref. Danijel Stojanović)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Partner/distributore Filtration Group Industrial e Amafilter (Premium Partner). Verificata: JV Hainzl (Austria), attiva a Belgrado dal 2023. Email ufficiale presente sul sito ma oscurata dallo strumento di estrazione, non riportabile con certezza - verificare manualmente.</t>
@@ -512,7 +511,6 @@
           <t>Jakka Group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Grad Beograd - Novi Beograd (Bulevar Zorana Đinđića 80)</t>
@@ -528,7 +526,6 @@
           <t>011/2600-901</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Veleprodaja attrezzature climatizzazione/ventilazione/riscaldamento. Verificata esistenza tramite directory planplus.rs (indirizzo/telefono coerenti). Fit settoriale parziale (HVAC generale piu' che dust collection specifico).</t>
@@ -546,7 +543,6 @@
           <t>Industrijska oprema (tehnološka rešenja za industrijski vazduh)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Grad Beograd - Zemun, Gornji grad (Banatska 28V)</t>
@@ -562,7 +558,6 @@
           <t>011/3077-086</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificata esistenza tramite planplus.rs. Ragione sociale esatta non confermata da fonte indipendente (nome sembra descrittivo) - consigliata verifica su registro APR prima di contatto commerciale.</t>
@@ -580,7 +575,6 @@
           <t>Tehnocon Filter</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Grad Beograd - Novi Beograd, Blok 9A (Bulevar maršala Tolbuhina 22)</t>
@@ -596,7 +590,6 @@
           <t>011/311-4042 ; 064/823-3229</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Filtri industriali per industria alimentare e farmaceutica. Verificata esistenza tramite planplus.rs. Nicchia alimentare/farmaceutica, adiacente al settore filtrazione aria industriale.</t>
@@ -646,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -656,7 +649,6 @@
           <t>Ecotip Tedex</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Grad Beograd - Zemun, Altina (Taška Načića 5B, 11283)</t>
@@ -672,7 +664,6 @@
           <t>011/2450-976</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Produzione/distribuzione filtri per aria e acqua. Parte del gruppo Ecotip (sede gruppo a Skopje), partner Aquaporin per purificazione acqua/aria nei Balcani dal 2021. Fonti: planplus.rs, amcham.mk.</t>
